--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q80_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q80_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009026490139764563</v>
+        <v>0.007996223890605442</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009026490139764563</v>
+        <v>0.007996223890605442</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003447366366155084</v>
+        <v>0.003098236696828226</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01671121251110549</v>
+        <v>0.01524010290918993</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01671121251110549</v>
+        <v>0.01524010290918993</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003138507826658058</v>
+        <v>0.00307456662087188</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03466374275824991</v>
+        <v>0.03150895102295732</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03466374275824991</v>
+        <v>0.03150895102295732</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005302976183980063</v>
+        <v>0.005131521513658307</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0583897573220354</v>
+        <v>0.0532018818421727</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0583897573220354</v>
+        <v>0.0532018818421727</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00615922116208233</v>
+        <v>0.005850243430226859</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.07175372865507414</v>
+        <v>0.06540226353350313</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07175372865507414</v>
+        <v>0.06540226353350313</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008510689670947045</v>
+        <v>0.007520375805669064</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07022535472597834</v>
+        <v>0.06388726893272316</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07022535472597834</v>
+        <v>0.06388726893272316</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009007983307878907</v>
+        <v>0.007431420764098975</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.06321637444509302</v>
+        <v>0.05755434187949425</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06321637444509302</v>
+        <v>0.05755434187949425</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008418082826414866</v>
+        <v>0.006845955369327877</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.05830214960349571</v>
+        <v>0.05315372706920574</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05830214960349571</v>
+        <v>0.05315372706920574</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008197972621585848</v>
+        <v>0.006796641763719034</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.05761273627973897</v>
+        <v>0.05258668108922445</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05761273627973897</v>
+        <v>0.05258668108922445</v>
       </c>
       <c r="D10" t="n">
-        <v>0.008551109456641167</v>
+        <v>0.007121898728593857</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.05239430966223873</v>
+        <v>0.04791870616294436</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05239430966223873</v>
+        <v>0.04791870616294436</v>
       </c>
       <c r="D11" t="n">
-        <v>0.008729842000940792</v>
+        <v>0.007311372077728299</v>
       </c>
     </row>
   </sheetData>
